--- a/314e-ig/output/StructureDefinition-slot-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-slot-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-slot-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-slot-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-slot-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-slot-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-slot-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-slot-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -567,7 +567,7 @@
     <t>Slot.schedule</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Schedule) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/schedule-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -970,7 +970,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.1171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="103.78515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/314e-ig/output/StructureDefinition-slot-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-slot-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-slot-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-slot-314e.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
